--- a/docs/data/raw/2026-05-24_ST.xlsx
+++ b/docs/data/raw/2026-05-24_ST.xlsx
@@ -536,36 +536,36 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>K152</t>
+          <t>L013</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>FLYING AMANI</t>
+          <t>PACKING GLORY</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J2" t="n">
         <v>135</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Z Purton</t>
+          <t>R Kingscote</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>D J Hall</t>
+          <t>P F Yiu</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>6/7/4/9/7/11</t>
+          <t>4/5/3/3/2/5</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -594,36 +594,36 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>G272</t>
+          <t>K438</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>YOUNG HORIZON</t>
+          <t>NYX GLUCK</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>K Teetan</t>
+          <t>C Williams</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>B Crawford</t>
+          <t>W K Mo</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>11/5/3/1/9/4</t>
+          <t>2/4/10/4/3/5</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -652,36 +652,36 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>K465</t>
+          <t>L031</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>YOUNG LEGACY</t>
+          <t>AKERMANIS GOLD</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>M Chadwick</t>
+          <t>E Brown</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>J Size</t>
+          <t>D Eustace</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>7/11/13/10/10/12</t>
+          <t>9/6/9/5/10/9</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -710,36 +710,36 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>H429</t>
+          <t>J123</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FRANTANCK</t>
+          <t>CALIFORNIA STAR</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>H Y Yuen (-10)</t>
+          <t>M Chadwick</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>P C Ng</t>
+          <t>A S Cruz</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4/4/5/12/12/6</t>
+          <t>10/12/7/2/1/3</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -768,36 +768,36 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>J459</t>
+          <t>K118</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>IRON LEGION</t>
+          <t>SUPER LOVE</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Y L Chung (-2)</t>
+          <t>L Ferraris</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>A S Cruz</t>
+          <t>C H Yip</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>12/10/13/1/7/8</t>
+          <t>4/11/14/5/14/8</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -826,36 +826,36 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>J162</t>
+          <t>L255</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SOARING BRONCO</t>
+          <t>GREEN ANGEL</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J7" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>J Orman</t>
+          <t>H Bowman</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>M Newnham</t>
+          <t>P C Ng</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3/2/1/10/12/5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -884,36 +884,36 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>K138</t>
+          <t>L178</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>GENERAL SMART</t>
+          <t>GUTSY BRAVO</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>J McDonald</t>
+          <t>J Orman</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>C S Shum</t>
+          <t>W Y So</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>12/13/2/5/6/7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -942,36 +942,36 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>K316</t>
+          <t>L266</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>HAPPY ALLIANCE</t>
+          <t>HAPPY PROMISE</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L Ferraris</t>
+          <t>J McDonald</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>K W Lui</t>
+          <t>D A Hayes</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>12/9/12/8/10/12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -1000,36 +1000,36 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>K110</t>
+          <t>L256</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>JOLLY JUMPER</t>
+          <t>Z PRINCE</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>H Bowman</t>
+          <t>M F Poon</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>W K Mo</t>
+          <t>D J Hall</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1/6/7/7/8/5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -1058,36 +1058,36 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>K044</t>
+          <t>K332</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>POWER SUMMIT</t>
+          <t>JUST FOLLOW ME</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>C L Chau (-2)</t>
+          <t>K Teetan</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>D Eustace</t>
+          <t>B Crawford</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>8/10/11/10/4/7</t>
+          <t>7/2/2/4/10/8</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -1116,36 +1116,36 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>H002</t>
+          <t>L087</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>PANDA LEGEND</t>
+          <t>GORGEOUS VICTORY</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>A Atzeni</t>
+          <t>Y L Chung (-2)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>W Y So</t>
+          <t>C S Shum</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>12/5/5/7/11/2</t>
+          <t>5/3/10/6/13</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -1174,19 +1174,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>K028</t>
+          <t>L026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ORIENTAL SURPRISE</t>
+          <t>GOLDEN WIN</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J13" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1195,15 +1195,15 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>D A Hayes</t>
+          <t>K L Man</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2/8/9/5/2/9</t>
+          <t>9/8/14/10</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -1232,36 +1232,36 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>H332</t>
+          <t>H283</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>HARRY'S HERO</t>
+          <t>DAILY TROPHY</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>H Bentley</t>
+          <t>J Moreira</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>P F Yiu</t>
+          <t>C Fownes</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3/6/6/2/2/5</t>
+          <t>7/8/7/11/13/13</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -1290,23 +1290,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>J003</t>
+          <t>K121</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>PERFECTO MOMENTS</t>
+          <t>COME FAST FAY FAY</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>M L Yeung</t>
+          <t>Z Purton</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1315,14 +1315,18 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4/4/8/3/5/5</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>5/7/2/1/6/3</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="n">
         <v>20</v>
       </c>
@@ -19403,36 +19407,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>K152</t>
+          <t>L013</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FLYING AMANI</t>
+          <t>PACKING GLORY</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
         <v>135</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Z Purton</t>
+          <t>R Kingscote</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>D J Hall</t>
+          <t>P F Yiu</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6/7/4/9/7/11</t>
+          <t>4/5/3/3/2/5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -19443,7 +19447,7 @@
         <v>14</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="3">
@@ -19454,36 +19458,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>G272</t>
+          <t>K438</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>YOUNG HORIZON</t>
+          <t>NYX GLUCK</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>K Teetan</t>
+          <t>C Williams</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>B Crawford</t>
+          <t>W K Mo</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11/5/3/1/9/4</t>
+          <t>2/4/10/4/3/5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -19494,7 +19498,7 @@
         <v>14</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="4">
@@ -19505,36 +19509,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>K465</t>
+          <t>L031</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>YOUNG LEGACY</t>
+          <t>AKERMANIS GOLD</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M Chadwick</t>
+          <t>E Brown</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>J Size</t>
+          <t>D Eustace</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7/11/13/10/10/12</t>
+          <t>9/6/9/5/10/9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -19545,7 +19549,7 @@
         <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="5">
@@ -19556,36 +19560,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H429</t>
+          <t>J123</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FRANTANCK</t>
+          <t>CALIFORNIA STAR</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>H Y Yuen (-10)</t>
+          <t>M Chadwick</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>P C Ng</t>
+          <t>A S Cruz</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4/4/5/12/12/6</t>
+          <t>10/12/7/2/1/3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -19596,7 +19600,7 @@
         <v>14</v>
       </c>
       <c r="M5" t="n">
-        <v>0.87</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="6">
@@ -19607,36 +19611,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J459</t>
+          <t>K118</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IRON LEGION</t>
+          <t>SUPER LOVE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Y L Chung (-2)</t>
+          <t>L Ferraris</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>A S Cruz</t>
+          <t>C H Yip</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12/10/13/1/7/8</t>
+          <t>4/11/14/5/14/8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -19647,7 +19651,7 @@
         <v>14</v>
       </c>
       <c r="M6" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -19658,36 +19662,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J162</t>
+          <t>L255</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SOARING BRONCO</t>
+          <t>GREEN ANGEL</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>J Orman</t>
+          <t>H Bowman</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>M Newnham</t>
+          <t>P C Ng</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3/2/1/10/12/5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -19698,7 +19702,7 @@
         <v>14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
@@ -19709,36 +19713,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>K138</t>
+          <t>L178</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GENERAL SMART</t>
+          <t>GUTSY BRAVO</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>J McDonald</t>
+          <t>J Orman</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C S Shum</t>
+          <t>W Y So</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12/13/2/5/6/7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -19749,7 +19753,7 @@
         <v>14</v>
       </c>
       <c r="M8" t="n">
-        <v>1.18</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="9">
@@ -19760,36 +19764,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>K316</t>
+          <t>L266</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HAPPY ALLIANCE</t>
+          <t>HAPPY PROMISE</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>L Ferraris</t>
+          <t>J McDonald</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>K W Lui</t>
+          <t>D A Hayes</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12/9/12/8/10/12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -19800,7 +19804,7 @@
         <v>14</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="10">
@@ -19811,36 +19815,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>K110</t>
+          <t>L256</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JOLLY JUMPER</t>
+          <t>Z PRINCE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>H Bowman</t>
+          <t>M F Poon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>W K Mo</t>
+          <t>D J Hall</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1/6/7/7/8/5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -19851,7 +19855,7 @@
         <v>14</v>
       </c>
       <c r="M10" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="11">
@@ -19862,36 +19866,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>K044</t>
+          <t>K332</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>POWER SUMMIT</t>
+          <t>JUST FOLLOW ME</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C L Chau (-2)</t>
+          <t>K Teetan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>D Eustace</t>
+          <t>B Crawford</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8/10/11/10/4/7</t>
+          <t>7/2/2/4/10/8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -19902,7 +19906,7 @@
         <v>14</v>
       </c>
       <c r="M11" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="12">
@@ -19913,36 +19917,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H002</t>
+          <t>L087</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PANDA LEGEND</t>
+          <t>GORGEOUS VICTORY</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>A Atzeni</t>
+          <t>Y L Chung (-2)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>W Y So</t>
+          <t>C S Shum</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12/5/5/7/11/2</t>
+          <t>5/3/10/6/13</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -19953,7 +19957,7 @@
         <v>14</v>
       </c>
       <c r="M12" t="n">
-        <v>0.96</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="13">
@@ -19964,19 +19968,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>K028</t>
+          <t>L026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ORIENTAL SURPRISE</t>
+          <t>GOLDEN WIN</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -19985,15 +19989,15 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>D A Hayes</t>
+          <t>K L Man</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2/8/9/5/2/9</t>
+          <t>9/8/14/10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -20004,7 +20008,7 @@
         <v>14</v>
       </c>
       <c r="M13" t="n">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="14">
@@ -20015,36 +20019,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H332</t>
+          <t>H283</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HARRY'S HERO</t>
+          <t>DAILY TROPHY</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>H Bentley</t>
+          <t>J Moreira</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>P F Yiu</t>
+          <t>C Fownes</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3/6/6/2/2/5</t>
+          <t>7/8/7/11/13/13</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -20055,7 +20059,7 @@
         <v>14</v>
       </c>
       <c r="M14" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="15">
@@ -20066,23 +20070,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>J003</t>
+          <t>K121</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PERFECTO MOMENTS</t>
+          <t>COME FAST FAY FAY</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>M L Yeung</t>
+          <t>Z Purton</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -20091,14 +20095,18 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4/4/8/3/5/5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>5/7/2/1/6/3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="n">
         <v>20</v>
       </c>
@@ -20106,7 +20114,7 @@
         <v>14</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9</v>
+        <v>1.04</v>
       </c>
     </row>
   </sheetData>
